--- a/Packages/cn.etetet.map/Luban/Config/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.map/Luban/Config/Datas/Unit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanghai/Documents/WOW/Packages/cn.etetet.wow/Luban/Config/Datas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanghai/Documents/WOW/Packages/cn.etetet.map/Luban/Config/Datas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A79317-26B2-CC4E-8B74-DDF1EB6BEBE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C558144-4CF1-CC43-A46C-BC95E2566186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4180" yWindow="440" windowWidth="38400" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -1049,7 +1049,7 @@
         <v>1009</v>
       </c>
       <c r="S6" s="1">
-        <v>300003</v>
+        <v>300001</v>
       </c>
       <c r="T6" s="5">
         <v>10021</v>
@@ -1143,7 +1143,7 @@
         <v>1009</v>
       </c>
       <c r="S7" s="1">
-        <v>300003</v>
+        <v>300001</v>
       </c>
       <c r="T7" s="5">
         <v>10021</v>
@@ -1237,7 +1237,7 @@
         <v>1009</v>
       </c>
       <c r="S8" s="1">
-        <v>300000</v>
+        <v>300001</v>
       </c>
       <c r="T8" s="5">
         <v>10021</v>
@@ -1856,11 +1856,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="H1:AK1"/>
     <mergeCell ref="H2:AK2"/>
     <mergeCell ref="H3:AK3"/>
@@ -1874,6 +1869,11 @@
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="N4:O4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="AB4:AC4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Packages/cn.etetet.map/Luban/Config/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.map/Luban/Config/Datas/Unit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanghai/Documents/WOW/Packages/cn.etetet.map/Luban/Config/Datas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C558144-4CF1-CC43-A46C-BC95E2566186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB62493-7E60-2440-876D-96C735670714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4180" yWindow="440" windowWidth="38400" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="65">
   <si>
     <t>##var</t>
   </si>
@@ -68,7 +68,7 @@
     <t>EClassType</t>
   </si>
   <si>
-    <t>map,int,long</t>
+    <t>map,NumericType,long</t>
   </si>
   <si>
     <t>##group</t>
@@ -98,6 +98,39 @@
     <t>职业</t>
   </si>
   <si>
+    <t>速度Base</t>
+  </si>
+  <si>
+    <t>半径Base</t>
+  </si>
+  <si>
+    <t>AOIBase</t>
+  </si>
+  <si>
+    <t>身高Base</t>
+  </si>
+  <si>
+    <t>体重Base</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>MaxHPBase</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>MaxMPBase</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
     <t>出生X坐标</t>
   </si>
   <si>
@@ -107,34 +140,10 @@
     <t>出生Z坐标</t>
   </si>
   <si>
-    <t>速度Base</t>
-  </si>
-  <si>
-    <t>半径Base</t>
-  </si>
-  <si>
-    <t>AOIBase</t>
-  </si>
-  <si>
-    <t>身高Base</t>
-  </si>
-  <si>
-    <t>体重Base</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>MaxHPBase</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>MaxMPBase</t>
-  </si>
-  <si>
-    <t>MP</t>
+    <t>出生面向</t>
+  </si>
+  <si>
+    <t>Player</t>
   </si>
   <si>
     <t>Mage</t>
@@ -149,21 +158,51 @@
     <t>法师</t>
   </si>
   <si>
+    <t>SpeedBase</t>
+  </si>
+  <si>
+    <t>RadiusBase</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>HeightBase</t>
+  </si>
+  <si>
+    <t>WeightBase</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>Yaw</t>
+  </si>
+  <si>
+    <t>Virtual</t>
+  </si>
+  <si>
+    <t>TrainingDummy</t>
+  </si>
+  <si>
+    <t>训练假人</t>
+  </si>
+  <si>
+    <t>UI-ChatIcon-Battlenet</t>
+  </si>
+  <si>
+    <t>死亡骑士</t>
+  </si>
+  <si>
     <t>Monster</t>
   </si>
   <si>
-    <t>TrainingDummy</t>
-  </si>
-  <si>
-    <t>训练假人</t>
-  </si>
-  <si>
-    <t>UI-ChatIcon-Battlenet</t>
-  </si>
-  <si>
-    <t>死亡骑士</t>
-  </si>
-  <si>
     <t>Boar</t>
   </si>
   <si>
@@ -182,43 +221,20 @@
     <t>牧师</t>
   </si>
   <si>
-    <t>Player</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>出生面向</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Virtual</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phase</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>NPC</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务NPC</t>
   </si>
   <si>
     <t>战士</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>任务NPC</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,13 +256,6 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -327,8 +336,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -338,9 +350,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -633,14 +642,20 @@
     <col min="10" max="10" width="5.1640625" customWidth="1"/>
     <col min="11" max="11" width="7.1640625" customWidth="1"/>
     <col min="12" max="12" width="6.1640625" customWidth="1"/>
-    <col min="13" max="13" width="7" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="5.1640625" customWidth="1"/>
+    <col min="13" max="13" width="8.6640625" customWidth="1"/>
+    <col min="14" max="14" width="10.33203125" customWidth="1"/>
+    <col min="15" max="15" width="5.1640625" customWidth="1"/>
     <col min="16" max="16" width="6.1640625" customWidth="1"/>
-    <col min="17" max="18" width="5.1640625" customWidth="1"/>
+    <col min="17" max="17" width="5.1640625" customWidth="1"/>
+    <col min="18" max="18" width="3.5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="2.83203125" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="2.83203125" bestFit="1" customWidth="1"/>
@@ -672,38 +687,38 @@
       <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14"/>
-      <c r="X1" s="14"/>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="14"/>
-      <c r="AA1" s="14"/>
-      <c r="AB1" s="14"/>
-      <c r="AC1" s="14"/>
-      <c r="AD1" s="14"/>
-      <c r="AE1" s="14"/>
-      <c r="AF1" s="14"/>
-      <c r="AG1" s="14"/>
-      <c r="AH1" s="14"/>
-      <c r="AI1" s="14"/>
-      <c r="AJ1" s="14"/>
-      <c r="AK1" s="14"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="10"/>
+      <c r="AD1" s="10"/>
+      <c r="AE1" s="10"/>
+      <c r="AF1" s="10"/>
+      <c r="AG1" s="10"/>
+      <c r="AH1" s="10"/>
+      <c r="AI1" s="10"/>
+      <c r="AJ1" s="10"/>
+      <c r="AK1" s="10"/>
     </row>
     <row r="2" spans="1:37">
       <c r="A2" t="s">
@@ -725,38 +740,38 @@
       <c r="G2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="14"/>
-      <c r="V2" s="14"/>
-      <c r="W2" s="14"/>
-      <c r="X2" s="14"/>
-      <c r="Y2" s="14"/>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="14"/>
-      <c r="AB2" s="14"/>
-      <c r="AC2" s="14"/>
-      <c r="AD2" s="14"/>
-      <c r="AE2" s="14"/>
-      <c r="AF2" s="14"/>
-      <c r="AG2" s="14"/>
-      <c r="AH2" s="14"/>
-      <c r="AI2" s="14"/>
-      <c r="AJ2" s="14"/>
-      <c r="AK2" s="14"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="10"/>
+      <c r="AC2" s="10"/>
+      <c r="AD2" s="10"/>
+      <c r="AE2" s="10"/>
+      <c r="AF2" s="10"/>
+      <c r="AG2" s="10"/>
+      <c r="AH2" s="10"/>
+      <c r="AI2" s="10"/>
+      <c r="AJ2" s="10"/>
+      <c r="AK2" s="10"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" t="s">
@@ -770,38 +785,38 @@
         <v>13</v>
       </c>
       <c r="G3" s="6"/>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="14"/>
-      <c r="AH3" s="14"/>
-      <c r="AI3" s="14"/>
-      <c r="AJ3" s="14"/>
-      <c r="AK3" s="14"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10"/>
+      <c r="AA3" s="10"/>
+      <c r="AB3" s="10"/>
+      <c r="AC3" s="10"/>
+      <c r="AD3" s="10"/>
+      <c r="AE3" s="10"/>
+      <c r="AF3" s="10"/>
+      <c r="AG3" s="10"/>
+      <c r="AH3" s="10"/>
+      <c r="AI3" s="10"/>
+      <c r="AJ3" s="10"/>
+      <c r="AK3" s="10"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" t="s">
@@ -825,64 +840,64 @@
       <c r="G4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="13"/>
+      <c r="L4" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" s="12"/>
+      <c r="N4" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="10"/>
-      <c r="J4" s="12" t="s">
+      <c r="O4" s="14"/>
+      <c r="P4" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="10" t="s">
+      <c r="Q4" s="12"/>
+      <c r="R4" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="11"/>
-      <c r="N4" s="12" t="s">
+      <c r="S4" s="14"/>
+      <c r="T4" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="O4" s="13"/>
-      <c r="P4" s="10" t="s">
+      <c r="U4" s="12"/>
+      <c r="V4" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="12" t="s">
+      <c r="W4" s="14"/>
+      <c r="X4" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="S4" s="13"/>
-      <c r="T4" s="10" t="s">
+      <c r="Y4" s="12"/>
+      <c r="Z4" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="U4" s="11"/>
-      <c r="V4" s="12" t="s">
+      <c r="AA4" s="14"/>
+      <c r="AB4" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="W4" s="13"/>
-      <c r="X4" s="10" t="s">
+      <c r="AC4" s="14"/>
+      <c r="AD4" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="Y4" s="11"/>
-      <c r="Z4" s="12" t="s">
+      <c r="AE4" s="13"/>
+      <c r="AF4" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="AA4" s="13"/>
-      <c r="AB4" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="AC4" s="13"/>
-      <c r="AD4" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE4" s="12"/>
-      <c r="AF4" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="AG4" s="10"/>
-      <c r="AH4" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="AI4" s="12"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI4" s="13"/>
       <c r="AJ4" s="15" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="AK4" s="15"/>
     </row>
@@ -891,106 +906,106 @@
         <v>1001</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="4">
-        <v>10001</v>
+        <v>40</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="I5" s="3">
         <v>6000</v>
       </c>
-      <c r="J5" s="5">
-        <v>10051</v>
+      <c r="J5" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="K5" s="3">
         <v>500</v>
       </c>
-      <c r="L5" s="4">
-        <v>10061</v>
+      <c r="L5" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="N5" s="5">
-        <v>10071</v>
+        <v>43</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="O5" s="3">
         <v>1780</v>
       </c>
-      <c r="P5" s="5">
-        <v>10081</v>
+      <c r="P5" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="Q5" s="3">
         <v>68000</v>
       </c>
-      <c r="R5" s="5">
-        <v>1009</v>
+      <c r="R5" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="S5" s="1">
         <v>0</v>
       </c>
-      <c r="T5" s="5">
-        <v>10021</v>
+      <c r="T5" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="U5" s="3">
         <v>1000</v>
       </c>
-      <c r="V5" s="5">
-        <v>1001</v>
+      <c r="V5" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="W5" s="3">
         <v>1000</v>
       </c>
-      <c r="X5" s="5">
-        <v>10041</v>
+      <c r="X5" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="Y5" s="3">
         <v>1000</v>
       </c>
-      <c r="Z5" s="5">
-        <v>1003</v>
+      <c r="Z5" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="AA5" s="3">
         <v>1000</v>
       </c>
-      <c r="AB5" s="5">
-        <v>1015</v>
+      <c r="AB5" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="AC5" s="1">
         <v>1</v>
       </c>
-      <c r="AD5" s="1">
-        <v>1010</v>
+      <c r="AD5" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="AE5" s="1">
         <v>0</v>
       </c>
-      <c r="AF5" s="1">
-        <v>1011</v>
+      <c r="AF5" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="AG5" s="1">
         <v>25200</v>
       </c>
-      <c r="AH5" s="4">
-        <v>1012</v>
+      <c r="AH5" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="AI5" s="1">
         <v>10000</v>
       </c>
-      <c r="AJ5" s="4">
-        <v>1014</v>
+      <c r="AJ5" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="AK5" s="1">
         <v>0</v>
@@ -1001,82 +1016,82 @@
         <v>1002</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="4">
-        <v>10001</v>
       </c>
       <c r="I6" s="3">
         <v>0</v>
       </c>
-      <c r="J6" s="5">
-        <v>10051</v>
+      <c r="J6" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="K6" s="3">
         <v>500</v>
       </c>
-      <c r="L6" s="4">
-        <v>10061</v>
+      <c r="L6" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="M6" s="3">
         <v>0</v>
       </c>
-      <c r="N6" s="5">
-        <v>10071</v>
+      <c r="N6" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="O6" s="3">
         <v>500</v>
       </c>
-      <c r="P6" s="5">
-        <v>10081</v>
+      <c r="P6" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="Q6" s="3">
         <v>30000</v>
       </c>
-      <c r="R6" s="5">
-        <v>1009</v>
+      <c r="R6" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="S6" s="1">
         <v>300001</v>
       </c>
-      <c r="T6" s="5">
-        <v>10021</v>
+      <c r="T6" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="U6" s="3">
         <v>100</v>
       </c>
-      <c r="V6" s="5">
-        <v>1001</v>
+      <c r="V6" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="W6" s="3">
         <v>100</v>
       </c>
-      <c r="X6" s="5">
-        <v>10041</v>
+      <c r="X6" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="Y6" s="3">
         <v>100</v>
       </c>
-      <c r="Z6" s="5">
-        <v>1003</v>
+      <c r="Z6" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="AA6" s="3">
         <v>100</v>
       </c>
-      <c r="AB6" s="5">
-        <v>1015</v>
+      <c r="AB6" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="AC6" s="1">
         <v>1</v>
@@ -1095,82 +1110,82 @@
         <v>1003</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7" s="4">
-        <v>10001</v>
       </c>
       <c r="I7" s="3">
         <v>0</v>
       </c>
-      <c r="J7" s="5">
-        <v>10051</v>
+      <c r="J7" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="K7" s="3">
         <v>500</v>
       </c>
-      <c r="L7" s="4">
-        <v>10061</v>
+      <c r="L7" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="M7" s="3">
         <v>0</v>
       </c>
-      <c r="N7" s="5">
-        <v>10071</v>
+      <c r="N7" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="O7" s="3">
         <v>500</v>
       </c>
-      <c r="P7" s="5">
-        <v>10081</v>
+      <c r="P7" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="Q7" s="3">
         <v>30000</v>
       </c>
-      <c r="R7" s="5">
-        <v>1009</v>
+      <c r="R7" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="S7" s="1">
         <v>300001</v>
       </c>
-      <c r="T7" s="5">
-        <v>10021</v>
+      <c r="T7" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="U7" s="3">
         <v>100</v>
       </c>
-      <c r="V7" s="5">
-        <v>1001</v>
+      <c r="V7" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="W7" s="3">
         <v>100</v>
       </c>
-      <c r="X7" s="5">
-        <v>10041</v>
+      <c r="X7" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="Y7" s="3">
         <v>100</v>
       </c>
-      <c r="Z7" s="5">
-        <v>1003</v>
+      <c r="Z7" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="AA7" s="3">
         <v>100</v>
       </c>
-      <c r="AB7" s="5">
-        <v>1015</v>
+      <c r="AB7" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="AC7" s="1">
         <v>1</v>
@@ -1189,82 +1204,82 @@
         <v>1004</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="4">
-        <v>10001</v>
       </c>
       <c r="I8" s="3">
         <v>2000</v>
       </c>
-      <c r="J8" s="5">
-        <v>10051</v>
+      <c r="J8" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="K8" s="3">
         <v>500</v>
       </c>
-      <c r="L8" s="4">
-        <v>10061</v>
+      <c r="L8" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="M8" s="3">
         <v>10000</v>
       </c>
-      <c r="N8" s="5">
-        <v>10071</v>
+      <c r="N8" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="O8" s="3">
         <v>500</v>
       </c>
-      <c r="P8" s="5">
-        <v>10081</v>
+      <c r="P8" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="Q8" s="3">
         <v>30000</v>
       </c>
-      <c r="R8" s="5">
-        <v>1009</v>
+      <c r="R8" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="S8" s="1">
         <v>300001</v>
       </c>
-      <c r="T8" s="5">
-        <v>10021</v>
+      <c r="T8" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="U8" s="3">
         <v>100</v>
       </c>
-      <c r="V8" s="5">
-        <v>1001</v>
+      <c r="V8" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="W8" s="3">
         <v>100</v>
       </c>
-      <c r="X8" s="5">
-        <v>10041</v>
+      <c r="X8" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="Y8" s="3">
         <v>100</v>
       </c>
-      <c r="Z8" s="5">
-        <v>1003</v>
+      <c r="Z8" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="AA8" s="3">
         <v>100</v>
       </c>
-      <c r="AB8" s="5">
-        <v>1015</v>
+      <c r="AB8" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="AC8" s="1">
         <v>1</v>
@@ -1283,78 +1298,78 @@
         <v>1005</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="H9" s="4">
-        <v>10001</v>
       </c>
       <c r="I9" s="3">
         <v>2000</v>
       </c>
-      <c r="J9" s="5">
-        <v>10051</v>
+      <c r="J9" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="K9" s="3">
         <v>500</v>
       </c>
-      <c r="L9" s="4">
-        <v>10061</v>
+      <c r="L9" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="M9" s="3">
         <v>10000</v>
       </c>
-      <c r="N9" s="5">
-        <v>10071</v>
+      <c r="N9" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="O9" s="3">
         <v>500</v>
       </c>
-      <c r="P9" s="5">
-        <v>10081</v>
+      <c r="P9" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="Q9" s="3">
         <v>30000</v>
       </c>
       <c r="R9" s="5"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="5">
-        <v>10021</v>
+      <c r="T9" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="U9" s="3">
         <v>100</v>
       </c>
-      <c r="V9" s="5">
-        <v>1001</v>
+      <c r="V9" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="W9" s="3">
         <v>100</v>
       </c>
-      <c r="X9" s="5">
-        <v>10041</v>
+      <c r="X9" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="Y9" s="3">
         <v>100</v>
       </c>
-      <c r="Z9" s="5">
-        <v>1003</v>
+      <c r="Z9" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="AA9" s="3">
         <v>100</v>
       </c>
-      <c r="AB9" s="5">
-        <v>1015</v>
+      <c r="AB9" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="AC9" s="1">
         <v>1</v>
@@ -1856,6 +1871,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="H1:AK1"/>
     <mergeCell ref="H2:AK2"/>
     <mergeCell ref="H3:AK3"/>
@@ -1872,8 +1889,6 @@
     <mergeCell ref="T4:U4"/>
     <mergeCell ref="V4:W4"/>
     <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="AB4:AC4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
